--- a/ejes/Políticas/Reportes Externos Subdirección Juventud 2026.xlsx
+++ b/ejes/Políticas/Reportes Externos Subdirección Juventud 2026.xlsx
@@ -32200,11 +32200,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Sacar este reporte de la petición de reporte de la PPDJ del producto 1.1.5 Jóvenes beneficiados con Transferencias Monetarias Condicionadas</t>
-        </is>
-      </c>
+      <c r="J2" s="6" t="n"/>
       <c r="K2" s="6" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -32265,11 +32261,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Preguntarle a DADE si en los listados de priorizados hay jóvenes raizales</t>
-        </is>
-      </c>
+      <c r="J3" s="6" t="n"/>
       <c r="K3" s="6" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -32332,7 +32324,7 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>La información es enviada directamente por DADE, quienes hacen el cruce con el RUV.</t>
+          <t>El reporte del Plan de Acción Distrital de víctimas se realiza con base en dos archivos. (i) La Subdirección de Diseño, Evaluación y Sistematización remite archivo de Excel con las cifras de las personas atendidas únicas víctimas de conflicto armado atendidas por la SDIS de manera trimestral. Dentro del archivo se identifican las cifras reportadas para el servicio Casas de Juventud y Forjar Restaurativo. La PUA víctimas se consolida a través del cruce de la ficha SIRBE de la SDIS, el reporte de víctimas elaborado por la Alta Consejería para las víctimas, Ingreso Mínimo Garantizado y reporte SISBEN IV de la Secretaría Distrital de Planeación. (ii) Para el caso de Jóvenes con Oportunidades, David Quiceno (del servicio Jóvenes con Oportunidades) remite archivo de Excel que reporta atención trimestral, y en la columna "M" se filtra la opción "Sí", para contabilizar número de jóvenes que durante el trimestre recibieron transferencia y están inscritos en el Registro Único de Víctimas.</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
@@ -32531,11 +32523,7 @@
       <c r="F3" s="6" t="n"/>
       <c r="G3" s="6" t="n"/>
       <c r="H3" s="6" t="n"/>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>El conteo se realiza sobre ingresos individuales al servicio Forjar Restaurativo de jóvenes por la comisión de delitos sexuales o contra la libertad y que cuentan con sanciones efectivas, y que pasan todas las fases de intervención señaladas.</t>
-        </is>
-      </c>
+      <c r="I3" s="6" t="n"/>
       <c r="J3" s="6" t="inlineStr">
         <is>
           <t>Semestral</t>
@@ -32593,11 +32581,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Duplicado dentro del ecosistema. Reportar a partir del reporte de la PP Infancia 1.1.11. Atención integral a adolescentes vinculados al Sistema de Responsabilidad Penal Adolescente (SRPA) en los servicios especializados de  la Secretaría Distrital de Integración Social </t>
-        </is>
-      </c>
+      <c r="I4" s="6" t="n"/>
       <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -32655,7 +32639,7 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>La información es enviada directamente por DADE, quienes hacen el cruce con el RUV.</t>
+          <t>El reporte del Plan de Acción Distrital de víctimas se realiza con base en dos archivos. (i) La Subdirección de Diseño, Evaluación y Sistematización remite archivo de Excel con las cifras de las personas atendidas únicas víctimas de conflicto armado atendidas por la SDIS de manera trimestral. Dentro del archivo se identifican las cifras reportadas para el servicio Casas de Juventud y Forjar Restaurativo. La PUA víctimas se consolida a través del cruce de la ficha SIRBE de la SDIS, el reporte de víctimas elaborado por la Alta Consejería para las víctimas, Ingreso Mínimo Garantizado y reporte SISBEN IV de la Secretaría Distrital de Planeación. (ii) Para el caso de Jóvenes con Oportunidades, David Quiceno (del servicio Jóvenes con Oportunidades) remite archivo de Excel que reporta atención trimestral, y en la columna "M" se filtra la opción "Sí", para contabilizar número de jóvenes que durante el trimestre recibieron transferencia y están inscritos en el Registro Único de Víctimas.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -32711,15 +32695,7 @@
         </is>
       </c>
       <c r="H6" s="8" t="n"/>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Se debe reportar toda la PUA de Forjar del año para jóvenes entre 14 y 17 años, desagregados por las siguientes variables para diligenciar el formato de reporte:
-Localidad (Suba, Rafael Uribe Uribe, Ciudad Bolívar)
-Sexo
-Discapacidad
-Grupo étnico</t>
-        </is>
-      </c>
+      <c r="I6" s="6" t="n"/>
       <c r="J6" s="8" t="inlineStr">
         <is>
           <t>Anual</t>
@@ -32777,12 +32753,7 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="I7" s="29" t="inlineStr">
-        <is>
-          <t>- FOR-PSS-298 Formato Base de Consolidación Mensual de Promoción en Estilos de Vida Saludable
-- FOR-PSS-545 Formato Reporte Trimestral Consolidado Cuantitativo y Cualitativo De Promoción De Hábitos En Estilos De Vida Saludable</t>
-        </is>
-      </c>
+      <c r="I7" s="29" t="n"/>
       <c r="J7" s="28" t="inlineStr">
         <is>
           <t>Cuando se demande</t>

--- a/ejes/Políticas/Reportes Externos Subdirección Juventud 2026.xlsx
+++ b/ejes/Políticas/Reportes Externos Subdirección Juventud 2026.xlsx
@@ -32475,11 +32475,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Petición directa del equipo de PP a Diego Forero. Solo adolescentes</t>
-        </is>
-      </c>
+      <c r="I2" s="6" t="n"/>
       <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Trimestral</t>

--- a/ejes/Políticas/Reportes Externos Subdirección Juventud 2026.xlsx
+++ b/ejes/Políticas/Reportes Externos Subdirección Juventud 2026.xlsx
@@ -1411,11 +1411,7 @@
           <t>1486 TALLERES INFORMATIVOS EN PREVENCIÓN.</t>
         </is>
       </c>
-      <c r="I6" s="37" t="inlineStr">
-        <is>
-          <t>En revisión con Daniela Correa - Profesional de enfoques diferenciales.</t>
-        </is>
-      </c>
+      <c r="I6" s="37" t="n"/>
       <c r="J6" s="37" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -1497,11 +1493,7 @@
 1506 PADRINAZGO PARA EL DESARROLLO DE EMPREDIMIENTO BANCO DE INSUMOS</t>
         </is>
       </c>
-      <c r="I7" s="37" t="inlineStr">
-        <is>
-          <t>En revisión con Daniela Correa - Profesional de enfoques diferenciales.</t>
-        </is>
-      </c>
+      <c r="I7" s="37" t="n"/>
       <c r="J7" s="37" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -1601,11 +1593,7 @@
 1505 VOLUNTARIADO INTERGENERACIONAL</t>
         </is>
       </c>
-      <c r="I8" s="37" t="inlineStr">
-        <is>
-          <t>En revisión con Daniela Correa - Profesional de enfoques diferenciales.</t>
-        </is>
-      </c>
+      <c r="I8" s="37" t="n"/>
       <c r="J8" s="37" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -2997,7 +2985,7 @@
       <c r="H24" s="41" t="n"/>
       <c r="I24" s="41" t="inlineStr">
         <is>
-          <t>En revisión con Daniela Correa - Profesional de enfoques diferenciales.</t>
+          <t>De SIRBE se pide toda la PUA de Casas y el reporte para cada política se realiza filtrando por la variable de pertenencia étnica. (En revisión con Daniela Correa.)</t>
         </is>
       </c>
       <c r="J24" s="37" t="inlineStr">
@@ -3102,7 +3090,7 @@
       </c>
       <c r="I25" s="37" t="inlineStr">
         <is>
-          <t>En revisión con Daniela Correa - Profesional de enfoques diferenciales.</t>
+          <t>De SIRBE se pide toda la PUA de Casas y el reporte para cada política se realiza filtrando por la variable de pertenencia étnica. (En revisión con Daniela Correa.)</t>
         </is>
       </c>
       <c r="J25" s="37" t="inlineStr">
@@ -32069,7 +32057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.85546875" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
@@ -32338,6 +32326,33 @@
       <c r="M4" s="6" t="inlineStr">
         <is>
           <t>No aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Política Pública</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Política Pública de Infancia y Adolescencia</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.2.8. Formación a niñas, niños, adolescentes y familias en derechos sexuales y derechos reproductivos con enfoque de género y diferencial.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Jóvenes Con Oportunidades</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Se solicita de forma trimestral al equipo de Jóvenes Con Oportunidades un reporte de los jóvenes entre 14 y 17 años que durante el trimestre culminaron el módulo 6 "Relaciones saludables y cuidadosas". Estos datos se agregan a la base de datos de evidencias en una pestaña separada, removiendo los tipos y números de documento de las personas, y solo se dejan datos de la ruta, primer nombre y primer apellido. En el reporte cuantitativo agregado del producto, estos datos se suman a los de la PUA de Casas de Juventud, de tal forma que el reporte cuantitativo y cualitativo sume lo realizado en Casas de Juventud y en Jóvenes con Oportunidades.</t>
         </is>
       </c>
     </row>
@@ -32691,7 +32706,11 @@
         </is>
       </c>
       <c r="H6" s="8" t="n"/>
-      <c r="I6" s="6" t="n"/>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>El reporte lo solicita anualmente la Subdirección para la Infancia de SDIS, y consta de dos documentos: una hoja de cálculo y un documento escrito. En la hoja de cálculo, hay que reportar la PUA de Forjar en el año, haciendo conteos combinados de Localidad, Edad (14, 15, 16, 17), Sexo, Tipo de Discapacidad, Pertenencia Étnica, Zona (Urbana o rural). Cada fila es una combinación de todas las variables anteriores. Para el reporte se pide la PUA de Forjar detallada, especificando las variables que se requieren para el reporte (por ejemplo, hay que pedir explícitamente la variable Zona, pues esta no viene por defecto en las PUA). En el documento escrito, se hace un breve análisis de la PUA, actualizando la evolución de adolescentes atendidos desde 2021, las modalidades de atención de la vigencia a reportar, el análisis del indicador, las acciones y resultados de la gestión que aportan al cumplimiento del indicador, y los aportes a la garantía de los derechos de ciudadanía y participación de niñas, niños y adolescentes.</t>
+        </is>
+      </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
           <t>Anual</t>
@@ -32919,11 +32938,7 @@
           <t>1486 TALLERES INFORMATIVOS EN PREVENCIÓN.</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>En revisión con Daniela Correa - Profesional de enfoques diferenciales.</t>
-        </is>
-      </c>
+      <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -32988,11 +33003,7 @@
 </t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>En revisión con Daniela Correa - Profesional de enfoques diferenciales.</t>
-        </is>
-      </c>
+      <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -33076,11 +33087,7 @@
 </t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>En revisión con Daniela Correa - Profesional de enfoques diferenciales.</t>
-        </is>
-      </c>
+      <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -33331,7 +33338,7 @@
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>En revisión con Daniela Correa - Profesional de enfoques diferenciales.</t>
+          <t>De SIRBE se pide toda la PUA de Casas y el reporte para cada política se realiza filtrando por la variable de pertenencia étnica. (En revisión con Daniela Correa.)</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -34423,7 +34430,7 @@
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>En revisión con Daniela Correa - Profesional de enfoques diferenciales.</t>
+          <t>De SIRBE se pide toda la PUA de Casas y el reporte para cada política se realiza filtrando por la variable de pertenencia étnica. (En revisión con Daniela Correa.)</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -35094,7 +35101,7 @@
       </c>
       <c r="I11" s="28" t="inlineStr">
         <is>
-          <t>En revisión con Daniela Correa - Profesional de enfoques diferenciales.</t>
+          <t>De SIRBE se pide toda la PUA de Casas y el reporte para cada política se realiza filtrando por la variable de pertenencia étnica. (En revisión con Daniela Correa.)</t>
         </is>
       </c>
       <c r="J11" s="28" t="inlineStr">

--- a/ejes/Políticas/Reportes Externos Subdirección Juventud 2026.xlsx
+++ b/ejes/Políticas/Reportes Externos Subdirección Juventud 2026.xlsx
@@ -51,7 +51,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +98,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3B0"/>
+        <bgColor rgb="00FFF3B0"/>
       </patternFill>
     </fill>
   </fills>
@@ -319,7 +325,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -506,6 +512,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2828,9 +2840,9 @@
 1505 VOLUNTARIADO INTERGENERACIONAL</t>
         </is>
       </c>
-      <c r="I22" s="37" t="inlineStr">
-        <is>
-          <t>En las solicitudes de ETL SIRBE agregar nombres y documentos en los números de caso a través de Diego Forero, y la petición se realiza a través del correo de Diego Duque</t>
+      <c r="I22" s="63" t="inlineStr">
+        <is>
+          <t>Se solicita matriz de datos PUA (extraído de SIRBE), se especifica la necesidad de incluir datos de pertenencia étnica. El reporte para cada política se realiza filtrando por la variable de pertenencia étnica. Se diligencian matrices enviadas por DADE.</t>
         </is>
       </c>
       <c r="J22" s="37" t="inlineStr">
@@ -2904,9 +2916,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="37" t="inlineStr">
-        <is>
-          <t>Se piden datos al equipo de jóvenes con oportunidades, quienes reportan autorreconocimiento. A partir de esos datos hacer doble validación</t>
+      <c r="I23" s="63" t="inlineStr">
+        <is>
+          <t>Se solicita matriz de datos PUA (extraído de SIRBE), se especifica la necesidad de incluir datos de pertenencia étnica. El reporte para cada política se realiza filtrando por la variable de pertenencia étnica. Se diligencian matrices enviadas por DADE.</t>
         </is>
       </c>
       <c r="J23" s="37" t="inlineStr">
@@ -3075,9 +3087,9 @@
 1505 VOLUNTARIADO INTERGENERACIONAL</t>
         </is>
       </c>
-      <c r="I25" s="37" t="inlineStr">
-        <is>
-          <t>De SIRBE se pide toda la PUA de Casas y el reporte para cada política se realiza filtrando por la variable de pertenencia étnica. &lt;strong&gt;(En revisión con Daniela Correa.)&lt;/strong&gt;</t>
+      <c r="I25" s="63" t="inlineStr">
+        <is>
+          <t>Se solicita matriz de datos PUA (extraído de SIRBE), se especifica la necesidad de incluir datos de pertenencia étnica. El reporte para cada política se realiza filtrando por la variable de pertenencia étnica. Se diligencian matrices enviadas por DADE.</t>
         </is>
       </c>
       <c r="J25" s="37" t="inlineStr">
@@ -3178,9 +3190,9 @@
 1505 VOLUNTARIADO INTERGENERACIONAL</t>
         </is>
       </c>
-      <c r="I26" s="37" t="inlineStr">
-        <is>
-          <t>Reportar autorreconocimiento. No se requiere aún doble validación, pero lo pueden solicitar las autoridades en cualquier momento</t>
+      <c r="I26" s="63" t="inlineStr">
+        <is>
+          <t>Se solicita matriz de datos PUA (extraído de SIRBE), se especifica la necesidad de incluir datos de pertenencia étnica. El reporte para cada política se realiza filtrando por la variable de pertenencia étnica. Se diligencian matrices enviadas por DADE.</t>
         </is>
       </c>
       <c r="J26" s="37" t="inlineStr">
@@ -32237,7 +32249,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J3" s="6" t="n"/>
+      <c r="J3" s="64" t="inlineStr">
+        <is>
+          <t>Se solicita matriz de datos PUA (extraído de SIRBE), se especifica la necesidad de incluir datos de pertenencia étnica. El reporte para cada política se realiza filtrando por la variable de pertenencia étnica. Se diligencian matrices enviadas por DADE.</t>
+        </is>
+      </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -33325,9 +33341,9 @@
       <c r="F8" s="61" t="n"/>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>De SIRBE se pide toda la PUA de Casas y el reporte para cada política se realiza filtrando por la variable de pertenencia étnica. &lt;strong&gt;(En revisión con Daniela Correa.)&lt;/strong&gt;</t>
+      <c r="I8" s="64" t="inlineStr">
+        <is>
+          <t>Se solicita matriz de datos PUA (extraído de SIRBE), se especifica la necesidad de incluir datos de pertenencia étnica. El reporte para cada política se realiza filtrando por la variable de pertenencia étnica. Se diligencian matrices enviadas por DADE.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
